--- a/output/full_scan/batch_seq8_2026-08-13.xlsx
+++ b/output/full_scan/batch_seq8_2026-08-13.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O125"/>
+  <dimension ref="A1:O126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1428,21 +1428,21 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>7714</v>
+        <v>7828</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>創泓科技</t>
+          <t>創新服務</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>577.7495977038947</v>
+        <v>583.4871358992715</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>157</v>
+        <v>1875</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>51.07217701651707</v>
+        <v>55.59839912515268</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>19.62936823551434</v>
+        <v>14.2616753825688</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.6814155651784227</v>
+        <v>1.07313834754898</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>-0.6971768440716493</v>
+        <v>34.23508555494773</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>7772</v>
+        <v>7714</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>耀穎</t>
+          <t>創泓科技</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>577.1589412843083</v>
+        <v>577.7495977038947</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>93.59999999999999</v>
+        <v>157</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,16 +1506,16 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>40.9488570486876</v>
+        <v>51.07217701651707</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>27.5676847642106</v>
+        <v>19.62936823551434</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.4980514892211411</v>
+        <v>0.6814155651784227</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>2.346925482921119</v>
+        <v>-0.6971768440716493</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6949</v>
+        <v>7772</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>沛爾生醫-創</t>
+          <t>耀穎</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>571.8605257451136</v>
+        <v>577.1589412843083</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>1020</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,16 +1559,16 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>60.3298217840586</v>
+        <v>40.9488570486876</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>26.10358839043392</v>
+        <v>27.5676847642106</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.7432855554058007</v>
+        <v>0.4980514892211411</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>8.987226932388864</v>
+        <v>2.346925482921119</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>7730</v>
+        <v>6949</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>暉盛-創</t>
+          <t>沛爾生醫-創</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>571.2530701099827</v>
+        <v>571.8605257451136</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>175</v>
+        <v>1020</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>57.39916226211051</v>
+        <v>60.3298217840586</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>23.32058037347104</v>
+        <v>26.10358839043392</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1.801264575546372</v>
+        <v>0.7432855554058007</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>0</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>2.842591089676712</v>
+        <v>8.987226932388864</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6955</v>
+        <v>7730</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>邦睿生技-創</t>
+          <t>暉盛-創</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>557.3642745551548</v>
+        <v>571.2530701099827</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>125.5</v>
+        <v>175</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,13 +1665,13 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>52.44249819606021</v>
+        <v>57.39916226211051</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>9.669683636575364</v>
+        <v>23.32058037347104</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.9921601090767432</v>
+        <v>1.801264575546372</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>1.246169687618979</v>
+        <v>2.842591089676712</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, breakout_20d, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>6952</v>
+        <v>6955</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>大武山</t>
+          <t>邦睿生技-創</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>547.4603751050295</v>
+        <v>557.3642745551548</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>38.4</v>
+        <v>125.5</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,13 +1718,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>62.2503048379131</v>
+        <v>52.44249819606021</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>29.42194243535372</v>
+        <v>9.669683636575364</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.6072972148856994</v>
+        <v>0.9921601090767432</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>0.4336743886463414</v>
+        <v>1.246169687618979</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, breakout_20d, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>8028</v>
+        <v>6952</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>昇陽半導體</t>
+          <t>大武山</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>544.0641464246469</v>
+        <v>547.4603751050295</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>267.5</v>
+        <v>38.4</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,13 +1771,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>45.92321671147409</v>
+        <v>62.2503048379131</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>17.03151113039235</v>
+        <v>29.42194243535372</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.8196703685371421</v>
+        <v>0.6072972148856994</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>0.08670671215031329</v>
+        <v>0.4336743886463414</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, kd_golden_cross, obv_uptrend</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>8016</v>
+        <v>8028</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>矽創</t>
+          <t>昇陽半導體</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>541.2221714938628</v>
+        <v>544.0641464246469</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>315.5</v>
+        <v>267.5</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>57.80810594516659</v>
+        <v>45.92321671147409</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>18.42241731961402</v>
+        <v>17.03151113039235</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>1.166746779422433</v>
+        <v>0.8196703685371421</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>4.426333927591577</v>
+        <v>0.08670671215031329</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6996</v>
+        <v>8016</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>力領科技</t>
+          <t>矽創</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>521.9851690795117</v>
+        <v>541.2221714938628</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>180</v>
+        <v>315.5</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>50.01560671404486</v>
+        <v>57.80810594516659</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>16.64351757335362</v>
+        <v>18.42241731961402</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.5590863160907471</v>
+        <v>1.166746779422433</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>1.193024443548762</v>
+        <v>4.426333927591577</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6937</v>
+        <v>6996</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>天虹</t>
+          <t>力領科技</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>519.35462945832</v>
+        <v>521.9851690795117</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>293.5</v>
+        <v>180</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,16 +1930,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>59.17773589026262</v>
+        <v>50.01560671404486</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>11.49242964564458</v>
+        <v>16.64351757335362</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>1.418122641109368</v>
+        <v>0.5590863160907471</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>4.611496506968765</v>
+        <v>1.193024443548762</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6861</v>
+        <v>6937</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>睿生光電</t>
+          <t>天虹</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>518.9737053300644</v>
+        <v>519.35462945832</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>220.5</v>
+        <v>293.5</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,13 +1983,13 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>45.48411655231417</v>
+        <v>59.17773589026262</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>26.33044262042425</v>
+        <v>11.49242964564458</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.7893924505471697</v>
+        <v>1.418122641109368</v>
       </c>
       <c r="K29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>7.183435365194391</v>
+        <v>4.611496506968765</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>6958</v>
+        <v>6861</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>日盛台駿</t>
+          <t>睿生光電</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>518.7609073432405</v>
+        <v>518.9737053300644</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>17.55</v>
+        <v>220.5</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,13 +2036,13 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>43.85437172730495</v>
+        <v>45.48411655231417</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>25.01570492306386</v>
+        <v>26.33044262042425</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.548050380118998</v>
+        <v>0.7893924505471697</v>
       </c>
       <c r="K30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>-0.1595024623946374</v>
+        <v>7.183435365194391</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>7810</v>
+        <v>6958</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>捷創科技</t>
+          <t>日盛台駿</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>512.4125378025818</v>
+        <v>518.7609073432405</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>200.5</v>
+        <v>17.55</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>55.02529570923995</v>
+        <v>43.85437172730495</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>16.8368026425107</v>
+        <v>25.01570492306386</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>3.616207110842907</v>
+        <v>0.548050380118998</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>2.396089978666038</v>
+        <v>-0.1595024623946374</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>7704</v>
+        <v>7810</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>明遠精密</t>
+          <t>捷創科技</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>506.1591094812642</v>
+        <v>512.4125378025818</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>62.3</v>
+        <v>200.5</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,16 +2142,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>57.62377916851619</v>
+        <v>55.02529570923995</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>23.6356088541181</v>
+        <v>16.8368026425107</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.3514495325631711</v>
+        <v>3.616207110842907</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>1.05629597555675</v>
+        <v>2.396089978666038</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>7855</v>
+        <v>7704</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>和運租車</t>
+          <t>明遠精密</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>488.2082515526226</v>
+        <v>506.1591094812642</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>44.35</v>
+        <v>62.3</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,13 +2195,13 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>17.89954099240408</v>
+        <v>57.62377916851619</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>26.26455423329302</v>
+        <v>23.6356088541181</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>3.720825155262262</v>
+        <v>0.3514495325631711</v>
       </c>
       <c r="K33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>-5.890099730882373</v>
+        <v>1.05629597555675</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>8039</v>
+        <v>7855</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>台虹</t>
+          <t>和運租車</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>482.084002811793</v>
+        <v>488.2082515526226</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>249.5</v>
+        <v>44.35</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,13 +2248,13 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>63.70412360547751</v>
+        <v>17.89954099240408</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>27.1120726701114</v>
+        <v>26.26455423329302</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.7813554874593469</v>
+        <v>3.720825155262262</v>
       </c>
       <c r="K34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>2.322115395204012</v>
+        <v>-5.890099730882373</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>7750</v>
+        <v>8039</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>新代</t>
+          <t>台虹</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>477.6361711011261</v>
+        <v>482.084002811793</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>2360</v>
+        <v>249.5</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>57.02653890342313</v>
+        <v>63.70412360547751</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>17.74339292854691</v>
+        <v>27.1120726701114</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.5250498536226856</v>
+        <v>0.7813554874593469</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>35.47176095720501</v>
+        <v>2.322115395204012</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>8040</v>
+        <v>7750</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>九暘</t>
+          <t>新代</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>470.7265936299896</v>
+        <v>477.6361711011261</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>74.2</v>
+        <v>2360</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>44.77732090870728</v>
+        <v>57.02653890342313</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>22.35752574595362</v>
+        <v>17.74339292854691</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.5711653265048038</v>
+        <v>0.5250498536226856</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>1.617173344736159</v>
+        <v>35.47176095720501</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>7556</v>
+        <v>8040</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>意德士</t>
+          <t>九暘</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>466.2226200414104</v>
+        <v>470.7265936299896</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>236.5</v>
+        <v>74.2</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>53.92859240658293</v>
+        <v>44.77732090870728</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>28.78735066332273</v>
+        <v>22.35752574595362</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.9928853331123836</v>
+        <v>0.5711653265048038</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>4.601068065562629</v>
+        <v>1.617173344736159</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, dealer_buy_3d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>7738</v>
+        <v>7556</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>東聯互動</t>
+          <t>意德士</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>458.6946806409758</v>
+        <v>466.2226200414104</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>170.5</v>
+        <v>236.5</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,16 +2460,16 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>56.03062681670932</v>
+        <v>53.92859240658293</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>33.77094712973146</v>
+        <v>28.78735066332273</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>1.457897811344477</v>
+        <v>0.9928853331123836</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>0.6748109032501062</v>
+        <v>4.601068065562629</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>7751</v>
+        <v>7738</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>竑騰</t>
+          <t>東聯互動</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>454.365354288362</v>
+        <v>458.6946806409758</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>1315</v>
+        <v>170.5</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,16 +2513,16 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>50.52756299234015</v>
+        <v>56.03062681670932</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>11.87745898949609</v>
+        <v>33.77094712973146</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.7053891661754931</v>
+        <v>1.457897811344477</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>19.25126592978442</v>
+        <v>0.6748109032501062</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6859</v>
+        <v>7751</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>伯特光</t>
+          <t>竑騰</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>453.2023261544873</v>
+        <v>454.365354288362</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>103.5</v>
+        <v>1315</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,16 +2566,16 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>47.27818235792986</v>
+        <v>50.52756299234015</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>24.60737445136873</v>
+        <v>11.87745898949609</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.5071958986284718</v>
+        <v>0.7053891661754931</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>1.310301513287256</v>
+        <v>19.25126592978442</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, bb_squeeze_breakout</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>6877</v>
+        <v>6859</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>鏵友益</t>
+          <t>伯特光</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>443.6224582098564</v>
+        <v>453.2023261544873</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>128.5</v>
+        <v>103.5</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,16 +2619,16 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>53.20551849745154</v>
+        <v>47.27818235792986</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>15.39283051698862</v>
+        <v>24.60737445136873</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.2515148523500305</v>
+        <v>0.5071958986284718</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>1.843221538595343</v>
+        <v>1.310301513287256</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, bb_squeeze_breakout</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6855</v>
+        <v>6877</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>數泓科</t>
+          <t>鏵友益</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>438.2966825348293</v>
+        <v>443.6224582098564</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>118.5</v>
+        <v>128.5</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,16 +2672,16 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>52.11636222030912</v>
+        <v>53.20551849745154</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>4.89391523719081</v>
+        <v>15.39283051698862</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.4442647760018243</v>
+        <v>0.2515148523500305</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>1.425867533313162</v>
+        <v>1.843221538595343</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6907</v>
+        <v>6855</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>雅特力-KY</t>
+          <t>數泓科</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>438.0258459570193</v>
+        <v>438.2966825348293</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>170.5</v>
+        <v>118.5</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,16 +2725,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>45.44848988516034</v>
+        <v>52.11636222030912</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>19.35929740583939</v>
+        <v>4.89391523719081</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1.293769680814559</v>
+        <v>0.4442647760018243</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>-2.863696264910012</v>
+        <v>1.425867533313162</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, dealer_buy_3d, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>7820</v>
+        <v>6907</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>立盈</t>
+          <t>雅特力-KY</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>428.93901222562</v>
+        <v>438.0258459570193</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>122</v>
+        <v>170.5</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,16 +2778,16 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>64.24287883609207</v>
+        <v>45.44848988516034</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>21.64400340963968</v>
+        <v>19.35929740583939</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.8260589525939036</v>
+        <v>1.293769680814559</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>3.011179316209703</v>
+        <v>-2.863696264910012</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, dealer_buy_3d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>7712</v>
+        <v>7820</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>博盛半導體</t>
+          <t>立盈</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>421.4692687630927</v>
+        <v>428.93901222562</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>146</v>
+        <v>122</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,13 +2831,13 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>48.20108274977657</v>
+        <v>64.24287883609207</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>19.87434057051541</v>
+        <v>21.64400340963968</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.6312306137277995</v>
+        <v>0.8260589525939036</v>
       </c>
       <c r="K45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>2.840601797705107</v>
+        <v>3.011179316209703</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6944</v>
+        <v>7712</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>兆聯實業</t>
+          <t>博盛半導體</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>415.8392170853291</v>
+        <v>421.4692687630927</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>755</v>
+        <v>146</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,13 +2884,13 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>40.3885994852041</v>
+        <v>48.20108274977657</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>23.82010490873874</v>
+        <v>19.87434057051541</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.3010225237416816</v>
+        <v>0.6312306137277995</v>
       </c>
       <c r="K46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>2.992949952388535</v>
+        <v>2.840601797705107</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>7823</v>
+        <v>6944</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>奧義賽博-KY創</t>
+          <t>兆聯實業</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>413.136852009764</v>
+        <v>415.8392170853291</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>85.3</v>
+        <v>755</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,13 +2937,13 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>56.02788899236798</v>
+        <v>40.3885994852041</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>16.59222567712868</v>
+        <v>23.82010490873874</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>1.677545358526954</v>
+        <v>0.3010225237416816</v>
       </c>
       <c r="K47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>0.657710505463635</v>
+        <v>2.992949952388535</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6919</v>
+        <v>7823</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>康霈*</t>
+          <t>奧義賽博-KY創</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>408.0300980087319</v>
+        <v>413.136852009764</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>104</v>
+        <v>85.3</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,13 +2990,13 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>48.24559206623086</v>
+        <v>56.02788899236798</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>18.28471199262086</v>
+        <v>16.59222567712868</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>1.583298814405334</v>
+        <v>1.677545358526954</v>
       </c>
       <c r="K48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.0624755967130203</v>
+        <v>0.657710505463635</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>7715</v>
+        <v>6919</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>裕山</t>
+          <t>康霈*</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>405.5425925819333</v>
+        <v>408.0300980087319</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>32</v>
+        <v>104</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>45.24501946070818</v>
+        <v>48.24559206623086</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>19.93945154037385</v>
+        <v>18.28471199262086</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>1.044568938666327</v>
+        <v>1.583298814405334</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-0.0278211411247027</v>
+        <v>0.0624755967130203</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>7717</v>
+        <v>7715</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>萊德光電-KY</t>
+          <t>裕山</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>397.4166159744239</v>
+        <v>405.5425925819333</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>428</v>
+        <v>32</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,16 +3096,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>48.39489146377178</v>
+        <v>45.24501946070818</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>21.21146728957275</v>
+        <v>19.93945154037385</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.8208055635345122</v>
+        <v>1.044568938666327</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>8.219902213357379</v>
+        <v>-0.0278211411247027</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>6965</v>
+        <v>7717</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>中傑-KY</t>
+          <t>萊德光電-KY</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>388.4442128479062</v>
+        <v>397.4166159744239</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>75.8</v>
+        <v>428</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>40.80696997618602</v>
+        <v>48.39489146377178</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>32.43660908229292</v>
+        <v>21.21146728957275</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>1.024349934055044</v>
+        <v>0.8208055635345122</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-0.1520971179372113</v>
+        <v>8.219902213357379</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>7402</v>
+        <v>6965</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>邑錡</t>
+          <t>中傑-KY</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>372.6296784437321</v>
+        <v>388.4442128479062</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>105</v>
+        <v>75.8</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,16 +3202,16 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>46.64897310496502</v>
+        <v>40.80696997618602</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>16.96404769832077</v>
+        <v>32.43660908229292</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.3443507850783456</v>
+        <v>1.024349934055044</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.0619217079374796</v>
+        <v>-0.1520971179372113</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>8033</v>
+        <v>7402</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>雷虎</t>
+          <t>邑錡</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>368.2609952787048</v>
+        <v>372.6296784437321</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>183.5</v>
+        <v>105</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>50.00441419733029</v>
+        <v>46.64897310496502</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>18.83619436346429</v>
+        <v>16.96404769832077</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>1.19611489459842</v>
+        <v>0.3443507850783456</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>-1.134045806891478</v>
+        <v>0.0619217079374796</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6902</v>
+        <v>8033</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>GOGOLOOK</t>
+          <t>雷虎</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>364.5067109909137</v>
+        <v>368.2609952787048</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>130</v>
+        <v>183.5</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,13 +3308,13 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>56.70472991294795</v>
+        <v>50.00441419733029</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>17.31826708798821</v>
+        <v>18.83619436346429</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>1.273681907483877</v>
+        <v>1.19611489459842</v>
       </c>
       <c r="K54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>1.502579130648521</v>
+        <v>-1.134045806891478</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>6870</v>
+        <v>6902</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>騰雲</t>
+          <t>GOGOLOOK</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>359.5492562936896</v>
+        <v>364.5067109909137</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>261.5</v>
+        <v>130</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>49.4744910612334</v>
+        <v>56.70472991294795</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>14.81073274451502</v>
+        <v>17.31826708798821</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.6721530477674825</v>
+        <v>1.273681907483877</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>1.284152198970899</v>
+        <v>1.502579130648521</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6903</v>
+        <v>6870</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>巨漢</t>
+          <t>騰雲</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>353.9581204242157</v>
+        <v>359.5492562936896</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>320.5</v>
+        <v>261.5</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>43.81039514371451</v>
+        <v>49.4744910612334</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>22.8135145351592</v>
+        <v>14.81073274451502</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.7353893239677353</v>
+        <v>0.6721530477674825</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>2.415907177022238</v>
+        <v>1.284152198970899</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>7822</v>
+        <v>6903</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>倍利科</t>
+          <t>巨漢</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>349.0257936253373</v>
+        <v>353.9581204242157</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>892</v>
+        <v>320.5</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,13 +3467,13 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>49.18717505874711</v>
+        <v>43.81039514371451</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>19.9027560382851</v>
+        <v>22.8135145351592</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>1.066979828095368</v>
+        <v>0.7353893239677353</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>18.62456942942088</v>
+        <v>2.415907177022238</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>6969</v>
+        <v>7822</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>成信實業*-創</t>
+          <t>倍利科</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>345.4281134644796</v>
+        <v>349.0257936253373</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>33.1</v>
+        <v>892</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,13 +3520,13 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>55.18821984964782</v>
+        <v>49.18717505874711</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>19.80875201587446</v>
+        <v>19.9027560382851</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.3440460094198224</v>
+        <v>1.066979828095368</v>
       </c>
       <c r="K58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-0.1188307585320211</v>
+        <v>18.62456942942088</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6899</v>
+        <v>6969</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>創為精密</t>
+          <t>成信實業*-創</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>334.0646021546164</v>
+        <v>345.4281134644796</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>50.6</v>
+        <v>33.1</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>38.25821300810704</v>
+        <v>55.18821984964782</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>21.19307648851413</v>
+        <v>19.80875201587446</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.7032201914708442</v>
+        <v>0.3440460094198224</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>0.3699792323237116</v>
+        <v>-0.1188307585320211</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>6967</v>
+        <v>6899</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>汎瑋材料</t>
+          <t>創為精密</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>333.8943927006212</v>
+        <v>334.0646021546164</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>70.5</v>
+        <v>50.6</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>49.21550448691527</v>
+        <v>38.25821300810704</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>14.79650882325239</v>
+        <v>21.19307648851413</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.1771250349129503</v>
+        <v>0.7032201914708442</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>0.049725449238627</v>
+        <v>0.3699792323237116</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6865</v>
+        <v>6967</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>偉康科技</t>
+          <t>汎瑋材料</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>333.7571684035363</v>
+        <v>333.8943927006212</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>25.3</v>
+        <v>70.5</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,13 +3679,13 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>51.41751128323764</v>
+        <v>49.21550448691527</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>7.810373058436814</v>
+        <v>14.79650882325239</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.5029922884110288</v>
+        <v>0.1771250349129503</v>
       </c>
       <c r="K61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.6797407536044265</v>
+        <v>0.049725449238627</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>8011</v>
+        <v>6865</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>台通</t>
+          <t>偉康科技</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>333.4683971174319</v>
+        <v>333.7571684035363</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>16.1</v>
+        <v>25.3</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>42.23089041419026</v>
+        <v>51.41751128323764</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>28.92294679223189</v>
+        <v>7.810373058436814</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.6108352729464148</v>
+        <v>0.5029922884110288</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.0513689304114844</v>
+        <v>0.6797407536044265</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6910</v>
+        <v>8011</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>德鴻</t>
+          <t>台通</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>330.9130645195828</v>
+        <v>333.4683971174319</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>25</v>
+        <v>16.1</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>45.43077926300381</v>
+        <v>42.23089041419026</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>24.16980371201315</v>
+        <v>28.92294679223189</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>1.1285149108885</v>
+        <v>0.6108352729464148</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,7 +3803,7 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>0.1922498478155484</v>
+        <v>0.0513689304114844</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
@@ -3813,21 +3813,21 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>7747</v>
+        <v>6910</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>昕奇雲端</t>
+          <t>德鴻</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>329.62573250324</v>
+        <v>330.9130645195828</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,13 +3838,13 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>41.5045592638267</v>
+        <v>45.43077926300381</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>16.38464500926267</v>
+        <v>24.16980371201315</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.4044282650974916</v>
+        <v>1.1285149108885</v>
       </c>
       <c r="K64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-7.478887097152697</v>
+        <v>0.1922498478155484</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6890</v>
+        <v>7747</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>來億-KY</t>
+          <t>昕奇雲端</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>329.444568131311</v>
+        <v>329.62573250324</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>177.5</v>
+        <v>0</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,13 +3891,13 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>47.96887153896499</v>
+        <v>41.5045592638267</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>12.44270405465581</v>
+        <v>16.38464500926267</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.6413794346745579</v>
+        <v>0.4044282650974916</v>
       </c>
       <c r="K65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>2.438702519639322</v>
+        <v>-7.478887097152697</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6951</v>
+        <v>6890</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>青新-創</t>
+          <t>來億-KY</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>328.6544022814096</v>
+        <v>329.444568131311</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>72.09999999999999</v>
+        <v>177.5</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>44.38504544874037</v>
+        <v>47.96887153896499</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>33.47729445530288</v>
+        <v>12.44270405465581</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.6303030303030303</v>
+        <v>0.6413794346745579</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.3789515775527139</v>
+        <v>2.438702519639322</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, cci_momentum</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>7827</v>
+        <v>6951</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>漢康-KY創</t>
+          <t>青新-創</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>327.9279155509223</v>
+        <v>328.6544022814096</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>159</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>53.70569697019789</v>
+        <v>44.38504544874037</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>14.31090491654441</v>
+        <v>33.47729445530288</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.6996509716425644</v>
+        <v>0.6303030303030303</v>
       </c>
       <c r="K67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>1.772941950445107</v>
+        <v>0.3789515775527139</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, cci_momentum</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>6901</v>
+        <v>7827</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>鑽石投資</t>
+          <t>漢康-KY創</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>325.2751303595075</v>
+        <v>327.9279155509223</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>17.35</v>
+        <v>159</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>50.6564718907354</v>
+        <v>53.70569697019789</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>18.42067370454617</v>
+        <v>14.31090491654441</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>1.000620300649836</v>
+        <v>0.6996509716425644</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,7 +4068,7 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>-0.0263973598733714</v>
+        <v>1.772941950445107</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
@@ -4078,21 +4078,21 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>7547</v>
+        <v>6901</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>碩網</t>
+          <t>鑽石投資</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>324.2801383876591</v>
+        <v>325.2751303595075</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>54.5</v>
+        <v>17.35</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>53.9765260158665</v>
+        <v>50.6564718907354</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>24.6420406771636</v>
+        <v>18.42067370454617</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.4975564410229103</v>
+        <v>1.000620300649836</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>1.097775979097243</v>
+        <v>-0.0263973598733714</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6962</v>
+        <v>7547</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>奕力-KY</t>
+          <t>碩網</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>321.8013283026776</v>
+        <v>324.2801383876591</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>33.7</v>
+        <v>54.5</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,16 +4156,16 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>52.13067077545429</v>
+        <v>53.9765260158665</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>22.2317983233836</v>
+        <v>24.6420406771636</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.928706509569018</v>
+        <v>0.4975564410229103</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.5228694357955641</v>
+        <v>1.097775979097243</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>7791</v>
+        <v>6962</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>皇家可口</t>
+          <t>奕力-KY</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>316.016334929006</v>
+        <v>321.8013283026776</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>58</v>
+        <v>33.7</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>23.41646714834356</v>
+        <v>52.13067077545429</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>28.35791265942161</v>
+        <v>22.2317983233836</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>4.752536780133006</v>
+        <v>0.928706509569018</v>
       </c>
       <c r="K71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>-0.1292248602455611</v>
+        <v>0.5228694357955641</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, liquidity_ok, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>7721</v>
+        <v>7791</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>微程式</t>
+          <t>皇家可口</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>311.6983184775201</v>
+        <v>316.016334929006</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>64.59999999999999</v>
+        <v>58</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>51.79155565153328</v>
+        <v>23.41646714834356</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>21.8457984005732</v>
+        <v>28.35791265942161</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.9040974656929872</v>
+        <v>4.752536780133006</v>
       </c>
       <c r="K72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>1.006529324068051</v>
+        <v>-0.1292248602455611</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, adx_trending, obv_uptrend</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6936</v>
+        <v>7721</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>永鴻生技</t>
+          <t>微程式</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>305.877544771459</v>
+        <v>311.6983184775201</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>32.1</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,13 +4315,13 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>49.39044554072822</v>
+        <v>51.79155565153328</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>15.0933879063162</v>
+        <v>21.8457984005732</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.516745614312265</v>
+        <v>0.9040974656929872</v>
       </c>
       <c r="K73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.0933718428291348</v>
+        <v>1.006529324068051</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>6953</v>
+        <v>6936</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>家碩</t>
+          <t>永鴻生技</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>305.6994129813008</v>
+        <v>305.877544771459</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>227.5</v>
+        <v>32.1</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,13 +4368,13 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>56.06521974510501</v>
+        <v>49.39044554072822</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>9.791362770497051</v>
+        <v>15.0933879063162</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>1.229909856450164</v>
+        <v>0.516745614312265</v>
       </c>
       <c r="K74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>2.564550083283775</v>
+        <v>0.0933718428291348</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, obv_uptrend, cci_momentum</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>7749</v>
+        <v>6953</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>意騰-KY</t>
+          <t>家碩</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>305.3512478650651</v>
+        <v>305.6994129813008</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>362</v>
+        <v>227.5</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>47.49533242309773</v>
+        <v>56.06521974510501</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>28.2597472930871</v>
+        <v>9.791362770497051</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.4991632468082274</v>
+        <v>1.229909856450164</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>7.148488328560809</v>
+        <v>2.564550083283775</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>rsi_strong, market_above_ma60, obv_uptrend, cci_momentum</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>7703</v>
+        <v>7749</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>銳澤</t>
+          <t>意騰-KY</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>299.3907028417268</v>
+        <v>305.3512478650651</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>180.5</v>
+        <v>362</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,13 +4474,13 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>49.2284298004738</v>
+        <v>47.49533242309773</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>16.95940816347779</v>
+        <v>28.2597472930871</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.4768590732741925</v>
+        <v>0.4991632468082274</v>
       </c>
       <c r="K76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>2.360369605121413</v>
+        <v>7.148488328560809</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>6887</v>
+        <v>7703</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>寶綠特-KY</t>
+          <t>銳澤</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>294.0740386935941</v>
+        <v>299.3907028417268</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>36.45</v>
+        <v>180.5</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>49.61804005837468</v>
+        <v>49.2284298004738</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>17.12459670717606</v>
+        <v>16.95940816347779</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.4594384836740967</v>
+        <v>0.4768590732741925</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-0.1919606776632632</v>
+        <v>2.360369605121413</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>6862</v>
+        <v>6887</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>三集瑞-KY</t>
+          <t>寶綠特-KY</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>293.8449561567587</v>
+        <v>294.0740386935941</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>148</v>
+        <v>36.45</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,13 +4580,13 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>46.97249681726899</v>
+        <v>49.61804005837468</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>18.56615253131344</v>
+        <v>17.12459670717606</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>1.345397832475639</v>
+        <v>0.4594384836740967</v>
       </c>
       <c r="K78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>3.337675241259181</v>
+        <v>-0.1919606776632632</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>7705</v>
+        <v>6862</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>三商餐飲</t>
+          <t>三集瑞-KY</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>292.6929322434067</v>
+        <v>293.8449561567587</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>30.05</v>
+        <v>148</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>42.80852474411822</v>
+        <v>46.97249681726899</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>20.99523185542612</v>
+        <v>18.56615253131344</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.6226348810396738</v>
+        <v>1.345397832475639</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.0545822026883956</v>
+        <v>3.337675241259181</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>7765</v>
+        <v>7705</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>中華資安</t>
+          <t>三商餐飲</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>292.1534279130741</v>
+        <v>292.6929322434067</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>226.5</v>
+        <v>30.05</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,13 +4686,13 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>50.45792467843792</v>
+        <v>42.80852474411822</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>15.82380223478507</v>
+        <v>20.99523185542612</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.5995173645915522</v>
+        <v>0.6226348810396738</v>
       </c>
       <c r="K80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.8153248090814218</v>
+        <v>0.0545822026883956</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>6983</v>
+        <v>7765</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>華洋精機</t>
+          <t>中華資安</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>288.1215441504061</v>
+        <v>292.1534279130741</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>299</v>
+        <v>226.5</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>39.0065681907889</v>
+        <v>50.45792467843792</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>11.11405970848021</v>
+        <v>15.82380223478507</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>1.273998629269435</v>
+        <v>0.5995173645915522</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>1.025544621953332</v>
+        <v>0.8153248090814218</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>8034</v>
+        <v>6983</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>榮群</t>
+          <t>華洋精機</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>286.1395994255125</v>
+        <v>288.1215441504061</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>18.85</v>
+        <v>299</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,16 +4792,16 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>37.66831985575124</v>
+        <v>39.0065681907889</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>36.07287909521452</v>
+        <v>11.11405970848021</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.4812369905666613</v>
+        <v>1.273998629269435</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.1108329264133465</v>
+        <v>1.025544621953332</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6947</v>
+        <v>8034</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>台鎔科技</t>
+          <t>榮群</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>282.9679739808636</v>
+        <v>286.1395994255125</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>74.59999999999999</v>
+        <v>18.85</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,16 +4845,16 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>42.27079493589067</v>
+        <v>37.66831985575124</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>16.87210162050686</v>
+        <v>36.07287909521452</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.2329287476476176</v>
+        <v>0.4812369905666613</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>0.4326328843361025</v>
+        <v>0.1108329264133465</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>6957</v>
+        <v>6947</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>裕慶-KY</t>
+          <t>台鎔科技</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>275.0255115018733</v>
+        <v>282.9679739808636</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>216.5</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,13 +4898,13 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>49.8920200751484</v>
+        <v>42.27079493589067</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>21.96780514324926</v>
+        <v>16.87210162050686</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.4692162533118001</v>
+        <v>0.2329287476476176</v>
       </c>
       <c r="K84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-2.266655506576928</v>
+        <v>0.4326328843361025</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>6994</v>
+        <v>6957</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>富威電力</t>
+          <t>裕慶-KY</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>273.9497618358039</v>
+        <v>275.0255115018733</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>35.9</v>
+        <v>216.5</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>30.76962397744011</v>
+        <v>49.8920200751484</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>37.69276793576809</v>
+        <v>21.96780514324926</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>1.114341215528425</v>
+        <v>0.4692162533118001</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,31 +4969,31 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>0.3625765026806427</v>
+        <v>-2.266655506576928</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>7734</v>
+        <v>6994</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>印能科技</t>
+          <t>富威電力</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>273.1300872525363</v>
+        <v>273.9497618358039</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>3250</v>
+        <v>35.9</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>49.48968151283652</v>
+        <v>30.76962397744011</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>9.228676887197331</v>
+        <v>37.69276793576809</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.776602199329163</v>
+        <v>1.114341215528425</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>0</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-8.843898356827665</v>
+        <v>0.3625765026806427</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>7732</v>
+        <v>7734</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>金興精密</t>
+          <t>印能科技</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>271.0527612388852</v>
+        <v>273.1300872525363</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>33.8</v>
+        <v>3250</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,13 +5057,13 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>47.72542598776971</v>
+        <v>49.48968151283652</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>3.735051574653912</v>
+        <v>9.228676887197331</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>2.713420714525077</v>
+        <v>0.776602199329163</v>
       </c>
       <c r="K87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-0.2602702578792828</v>
+        <v>-8.843898356827665</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6885</v>
+        <v>7732</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>全福生技</t>
+          <t>金興精密</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>270.369757564987</v>
+        <v>271.0527612388852</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>21</v>
+        <v>33.8</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>49.10334395142381</v>
+        <v>47.72542598776971</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>11.86519394052046</v>
+        <v>3.735051574653912</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>1.641767647878674</v>
+        <v>2.713420714525077</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.0448061235347104</v>
+        <v>-0.2602702578792828</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>volume_break, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>7821</v>
+        <v>6885</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>神數</t>
+          <t>全福生技</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>269.6150884379167</v>
+        <v>270.369757564987</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>39.4</v>
+        <v>21</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>39.4509339900339</v>
+        <v>49.10334395142381</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>17.19026883774717</v>
+        <v>11.86519394052046</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>1.473218562149188</v>
+        <v>1.641767647878674</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.0697207250155385</v>
+        <v>0.0448061235347104</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6924</v>
+        <v>7821</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>榮惠-KY創</t>
+          <t>神數</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>260.4349492560391</v>
+        <v>269.6150884379167</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>114.5</v>
+        <v>39.4</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,13 +5216,13 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>52.04742711442906</v>
+        <v>39.4509339900339</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>17.2652498655762</v>
+        <v>17.19026883774717</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.975372060163482</v>
+        <v>1.473218562149188</v>
       </c>
       <c r="K90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>2.293883058189625</v>
+        <v>0.0697207250155385</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>7839</v>
+        <v>6924</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>達人網</t>
+          <t>榮惠-KY創</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>258.8770524649008</v>
+        <v>260.4349492560391</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>45.75</v>
+        <v>114.5</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,16 +5269,16 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>49.17563588165896</v>
+        <v>52.04742711442906</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>14.50756487697863</v>
+        <v>17.2652498655762</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.6959228411366318</v>
+        <v>0.975372060163482</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.2638760261166837</v>
+        <v>2.293883058189625</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>7780</v>
+        <v>7839</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>大研生醫*</t>
+          <t>達人網</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>250.8965163225449</v>
+        <v>258.8770524649008</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>16.7</v>
+        <v>45.75</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,16 +5322,16 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>35.9838111007401</v>
+        <v>49.17563588165896</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>33.63669040760568</v>
+        <v>14.50756487697863</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>1.125247884586517</v>
+        <v>0.6959228411366318</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>0.0377427105754311</v>
+        <v>0.2638760261166837</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>8032</v>
+        <v>7780</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>光菱</t>
+          <t>大研生醫*</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>249.1727889876661</v>
+        <v>250.8965163225449</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>37.05</v>
+        <v>16.7</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>46.58941052371798</v>
+        <v>35.9838111007401</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>25.39946355253957</v>
+        <v>33.63669040760568</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.5904353324442583</v>
+        <v>1.125247884586517</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,7 +5393,7 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.5248204147715785</v>
+        <v>0.0377427105754311</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
@@ -5403,21 +5403,21 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>7768</v>
+        <v>8032</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>頌勝科技</t>
+          <t>光菱</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>247.3136203947638</v>
+        <v>249.1727889876661</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>280</v>
+        <v>37.05</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>47.10271111619146</v>
+        <v>46.58941052371798</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>42.46925804357605</v>
+        <v>25.39946355253957</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>1.120172829122258</v>
+        <v>0.5904353324442583</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>4.943137987382393</v>
+        <v>0.5248204147715785</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>7818</v>
+        <v>7768</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>溢泰實業</t>
+          <t>頌勝科技</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>246.835388407464</v>
+        <v>247.3136203947638</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>63.3</v>
+        <v>280</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>37.90233886272883</v>
+        <v>47.10271111619146</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>30.22953632694102</v>
+        <v>42.46925804357605</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.4859074304414517</v>
+        <v>1.120172829122258</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.0976595376936033</v>
+        <v>4.943137987382393</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>7722</v>
+        <v>7818</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>LINEPAY</t>
+          <t>溢泰實業</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>244.6551765520024</v>
+        <v>246.835388407464</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>290.5</v>
+        <v>63.3</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>49.21068604812951</v>
+        <v>37.90233886272883</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>21.73396196419279</v>
+        <v>30.22953632694102</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.5402717308929691</v>
+        <v>0.4859074304414517</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>2.252221237927266</v>
+        <v>-0.0976595376936033</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>7842</v>
+        <v>7722</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>天能綠電</t>
+          <t>LINEPAY</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>239.2709087440436</v>
+        <v>244.6551765520024</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>89</v>
+        <v>290.5</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>51.04168449365672</v>
+        <v>49.21068604812951</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>10.73447676743741</v>
+        <v>21.73396196419279</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>1.517979787508137</v>
+        <v>0.5402717308929691</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>1.994057822271981</v>
+        <v>2.252221237927266</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, obv_uptrend</t>
+          <t>market_above_ma60, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6988</v>
+        <v>7842</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>威力暘-創</t>
+          <t>天能綠電</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>235.0717824410295</v>
+        <v>239.2709087440436</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>12.5</v>
+        <v>89</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>50.08359029209468</v>
+        <v>51.04168449365672</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>10.51900848703302</v>
+        <v>10.73447676743741</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>1.401476450397534</v>
+        <v>1.517979787508137</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>0.2268095772512834</v>
+        <v>1.994057822271981</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>8024</v>
+        <v>6988</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>佑華</t>
+          <t>威力暘-創</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>234.6940434935028</v>
+        <v>235.0717824410295</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>13.75</v>
+        <v>12.5</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,16 +5693,16 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>41.78513827731791</v>
+        <v>50.08359029209468</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>15.2257154123945</v>
+        <v>10.51900848703302</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.6343391170135179</v>
+        <v>1.401476450397534</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.1260174169423177</v>
+        <v>0.2268095772512834</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6923</v>
+        <v>8024</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>中台</t>
+          <t>佑華</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>222.783031122995</v>
+        <v>234.6940434935028</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>76.59999999999999</v>
+        <v>13.75</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,16 +5746,16 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>50.35829362224407</v>
+        <v>41.78513827731791</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>9.693167297481491</v>
+        <v>15.2257154123945</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.4729390280475947</v>
+        <v>0.6343391170135179</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>0.1190120512841847</v>
+        <v>-0.1260174169423177</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>6894</v>
+        <v>6923</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>衛司特</t>
+          <t>中台</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>211.1496777315664</v>
+        <v>222.783031122995</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>338.5</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,16 +5799,16 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>49.14883644951831</v>
+        <v>50.35829362224407</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>14.19958916212614</v>
+        <v>9.693167297481491</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>1.095365549607685</v>
+        <v>0.4729390280475947</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>2.620511404012554</v>
+        <v>0.1190120512841847</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6928</v>
+        <v>6894</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>攸泰科技</t>
+          <t>衛司特</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>208.3330938410607</v>
+        <v>211.1496777315664</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>49.3</v>
+        <v>338.5</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,16 +5852,16 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>48.77225502042197</v>
+        <v>49.14883644951831</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>13.68082070331631</v>
+        <v>14.19958916212614</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.218897570593396</v>
+        <v>1.095365549607685</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.0917151104553896</v>
+        <v>2.620511404012554</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>6908</v>
+        <v>6928</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>宏碁遊戲-創</t>
+          <t>攸泰科技</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>207.5029009066881</v>
+        <v>208.3330938410607</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>33.25</v>
+        <v>49.3</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>40.58763305533159</v>
+        <v>48.77225502042197</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>31.98304557772932</v>
+        <v>13.68082070331631</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.7204348165167886</v>
+        <v>0.218897570593396</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>0.0824530013314301</v>
+        <v>-0.0917151104553896</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6916</v>
+        <v>6908</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>華凌</t>
+          <t>宏碁遊戲-創</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>207.0395054309559</v>
+        <v>207.5029009066881</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>18.65</v>
+        <v>33.25</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>47.19440391146001</v>
+        <v>40.58763305533159</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>13.09800789329798</v>
+        <v>31.98304557772932</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.4009277572489383</v>
+        <v>0.7204348165167886</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.1010442285020847</v>
+        <v>0.0824530013314301</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>6873</v>
+        <v>6916</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>泓德能源</t>
+          <t>華凌</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>205.6360075073711</v>
+        <v>207.0395054309559</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>70.59999999999999</v>
+        <v>18.65</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>29.85937068123515</v>
+        <v>47.19440391146001</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>19.7493556871331</v>
+        <v>13.09800789329798</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>3.317780015688625</v>
+        <v>0.4009277572489383</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>-0.7558221964419669</v>
+        <v>0.1010442285020847</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>6854</v>
+        <v>6873</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>錼創科技-KY創</t>
+          <t>泓德能源</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>192.4060643153241</v>
+        <v>205.6360075073711</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>94</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>38.14888682829686</v>
+        <v>29.85937068123515</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>36.82751876059486</v>
+        <v>19.7493556871331</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.3507903457042381</v>
+        <v>3.317780015688625</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>1.49772872278</v>
+        <v>-0.7558221964419669</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>6909</v>
+        <v>6854</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>創控</t>
+          <t>錼創科技-KY創</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>178.7536846742425</v>
+        <v>192.4060643153241</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>41.6</v>
+        <v>94</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>42.89719386251225</v>
+        <v>38.14888682829686</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>26.64732208383663</v>
+        <v>36.82751876059486</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.4764056086609184</v>
+        <v>0.3507903457042381</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,7 +6135,7 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>0.5550839448337532</v>
+        <v>1.49772872278</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
@@ -6145,21 +6145,21 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>7740</v>
+        <v>6909</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>熙特爾-創</t>
+          <t>創控</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>171.3561892699808</v>
+        <v>178.7536846742425</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>143</v>
+        <v>41.6</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>43.91156300848477</v>
+        <v>42.89719386251225</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>18.15235889742602</v>
+        <v>26.64732208383663</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>1.065143531931289</v>
+        <v>0.4764056086609184</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>0.4125887667136639</v>
+        <v>0.5550839448337532</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6918</v>
+        <v>7740</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>愛派司</t>
+          <t>熙特爾-創</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>166.6908596210709</v>
+        <v>171.3561892699808</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>73</v>
+        <v>143</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>53.12826194006902</v>
+        <v>43.91156300848477</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>18.39848396115534</v>
+        <v>18.15235889742602</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.7885388242633853</v>
+        <v>1.065143531931289</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,7 +6241,7 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.3058315680008057</v>
+        <v>0.4125887667136639</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
@@ -6251,21 +6251,21 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>7728</v>
+        <v>6918</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>光焱科技</t>
+          <t>愛派司</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>165.608686635329</v>
+        <v>166.6908596210709</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>594</v>
+        <v>73</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,16 +6276,16 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>44.9048236290129</v>
+        <v>53.12826194006902</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>17.52318325217685</v>
+        <v>18.39848396115534</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.3554456223544002</v>
+        <v>0.7885388242633853</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L110" s="2" t="n">
         <v>0</v>
@@ -6294,7 +6294,7 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>5.089823058606918</v>
+        <v>0.3058315680008057</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
@@ -6304,21 +6304,21 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>7689</v>
+        <v>7728</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>大鵬科CLMX</t>
+          <t>光焱科技</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>164.1069015375267</v>
+        <v>165.608686635329</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>174</v>
+        <v>594</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,16 +6329,16 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>31.17061066973896</v>
+        <v>44.9048236290129</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>31.59200061719794</v>
+        <v>17.52318325217685</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.4745732337636509</v>
+        <v>0.3554456223544002</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>1.365107884935668</v>
+        <v>5.089823058606918</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>7803</v>
+        <v>7689</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>雲象科技-創</t>
+          <t>大鵬科CLMX</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>163.4748288525862</v>
+        <v>164.1069015375267</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>19.65</v>
+        <v>174</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>38.66520300994409</v>
+        <v>31.17061066973896</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>20.45587294902399</v>
+        <v>31.59200061719794</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.1672577867738134</v>
+        <v>0.4745732337636509</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.071879473237512</v>
+        <v>1.365107884935668</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>8038</v>
+        <v>7803</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>長園科</t>
+          <t>雲象科技-創</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>160.1816642382411</v>
+        <v>163.4748288525862</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>32</v>
+        <v>19.65</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,16 +6435,16 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>35.89040183858263</v>
+        <v>38.66520300994409</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>20.75056367165069</v>
+        <v>20.45587294902399</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.6953046963271055</v>
+        <v>0.1672577867738134</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L113" s="2" t="n">
         <v>0</v>
@@ -6453,7 +6453,7 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>0.1430848237246289</v>
+        <v>0.071879473237512</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
@@ -6463,21 +6463,21 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>6971</v>
+        <v>8038</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>惠民實業</t>
+          <t>長園科</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>159.8702299329946</v>
+        <v>160.1816642382411</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>25.3</v>
+        <v>32</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,16 +6488,16 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>30.22219074052516</v>
+        <v>35.89040183858263</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>18.99516126758592</v>
+        <v>20.75056367165069</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>1.673463794925051</v>
+        <v>0.6953046963271055</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.0429011295984313</v>
+        <v>0.1430848237246289</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>6869</v>
+        <v>6971</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>雲豹能源</t>
+          <t>惠民實業</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>158.745683600115</v>
+        <v>159.8702299329946</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>66.59999999999999</v>
+        <v>25.3</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,13 +6541,13 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>42.17097829585253</v>
+        <v>30.22219074052516</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>16.77865202598346</v>
+        <v>18.99516126758592</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.4579564480074847</v>
+        <v>1.673463794925051</v>
       </c>
       <c r="K115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>0.4229253757445161</v>
+        <v>-0.0429011295984313</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>volume_break, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>6997</v>
+        <v>6869</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>博弘</t>
+          <t>雲豹能源</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>154.4023208432825</v>
+        <v>158.745683600115</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>0</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,13 +6594,13 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>43.11968132994374</v>
+        <v>42.17097829585253</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>11.53644391679057</v>
+        <v>16.77865202598346</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0</v>
+        <v>0.4579564480074847</v>
       </c>
       <c r="K116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-3.804781350328589</v>
+        <v>0.4229253757445161</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>7786</v>
+        <v>6997</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>東方風能</t>
+          <t>博弘</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>152.6092412088329</v>
+        <v>154.4023208432825</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,13 +6647,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>48.296348732833</v>
+        <v>43.11968132994374</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>15.20754985258452</v>
+        <v>11.53644391679057</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>1.03228857806302</v>
+        <v>0</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>0</v>
@@ -6665,7 +6665,7 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>0.2985245819479099</v>
+        <v>-3.804781350328589</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
@@ -6675,21 +6675,21 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>6895</v>
+        <v>7786</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>宏碩系統</t>
+          <t>東方風能</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>151.8419503561367</v>
+        <v>152.6092412088329</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,13 +6700,13 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>38.42993436902537</v>
+        <v>48.296348732833</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>23.06215935503015</v>
+        <v>15.20754985258452</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.8433157076266554</v>
+        <v>1.03228857806302</v>
       </c>
       <c r="K118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>1.304957883465146</v>
+        <v>0.2985245819479099</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>7799</v>
+        <v>6895</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>禾榮科</t>
+          <t>宏碩系統</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>147.1892241639418</v>
+        <v>151.8419503561367</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>365</v>
+        <v>118</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,13 +6753,13 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>46.07287355379689</v>
+        <v>38.42993436902537</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>19.00321481657365</v>
+        <v>23.06215935503015</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.251226299333295</v>
+        <v>0.8433157076266554</v>
       </c>
       <c r="K119" s="2" t="n">
         <v>0</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-0.4723151494652171</v>
+        <v>1.304957883465146</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>7760</v>
+        <v>7799</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>享溫馨</t>
+          <t>禾榮科</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>133.725803384346</v>
+        <v>147.1892241639418</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>33</v>
+        <v>365</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,13 +6806,13 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>42.80830032081736</v>
+        <v>46.07287355379689</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>13.2539184437095</v>
+        <v>19.00321481657365</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.1084883013567092</v>
+        <v>0.251226299333295</v>
       </c>
       <c r="K120" s="2" t="n">
         <v>0</v>
@@ -6824,31 +6824,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>-0.1690672794219724</v>
+        <v>-0.4723151494652171</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>7770</v>
+        <v>7760</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>君曜</t>
+          <t>享溫馨</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>129.0997445503666</v>
+        <v>133.725803384346</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>39.75</v>
+        <v>33</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,13 +6859,13 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>52.2866156000043</v>
+        <v>42.80830032081736</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>11.38662630353114</v>
+        <v>13.2539184437095</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.4331029746319269</v>
+        <v>0.1084883013567092</v>
       </c>
       <c r="K121" s="2" t="n">
         <v>0</v>
@@ -6877,31 +6877,31 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>1.557872437783229</v>
+        <v>-0.1690672794219724</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>6925</v>
+        <v>7770</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>意藍</t>
+          <t>君曜</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>109.6937616987318</v>
+        <v>129.0997445503666</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>53.7</v>
+        <v>39.75</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,13 +6912,13 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>44.4735818187801</v>
+        <v>52.2866156000043</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>14.28637697940448</v>
+        <v>11.38662630353114</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.5475913398212208</v>
+        <v>0.4331029746319269</v>
       </c>
       <c r="K122" s="2" t="n">
         <v>0</v>
@@ -6930,31 +6930,31 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>0.5346058969333114</v>
+        <v>1.557872437783229</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>7736</v>
+        <v>6925</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>虎山</t>
+          <t>意藍</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>87.96857949495654</v>
+        <v>109.6937616987318</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>69.59999999999999</v>
+        <v>53.7</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,13 +6965,13 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>40.29083250683689</v>
+        <v>44.4735818187801</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>16.07531860711915</v>
+        <v>14.28637697940448</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.6973740852346104</v>
+        <v>0.5475913398212208</v>
       </c>
       <c r="K123" s="2" t="n">
         <v>0</v>
@@ -6983,7 +6983,7 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>0.0182308652181989</v>
+        <v>0.5346058969333114</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
@@ -6993,21 +6993,21 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>7753</v>
+        <v>7736</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>星亞</t>
+          <t>虎山</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>69.0142092283797</v>
+        <v>87.96857949495654</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>37.5</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,13 +7018,13 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>40.28520065679835</v>
+        <v>40.29083250683689</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>11.07454660496245</v>
+        <v>16.07531860711915</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.2109191874667864</v>
+        <v>0.6973740852346104</v>
       </c>
       <c r="K124" s="2" t="n">
         <v>0</v>
@@ -7036,7 +7036,7 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>0.0521032783380719</v>
+        <v>0.0182308652181989</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
@@ -7046,52 +7046,105 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
+        <v>7753</v>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>星亞</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D125" s="2" t="n">
+        <v>69.0142092283797</v>
+      </c>
+      <c r="E125" s="2" t="n">
+        <v>37.5</v>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H125" s="2" t="n">
+        <v>40.28520065679835</v>
+      </c>
+      <c r="I125" s="2" t="n">
+        <v>11.07454660496245</v>
+      </c>
+      <c r="J125" s="2" t="n">
+        <v>0.2109191874667864</v>
+      </c>
+      <c r="K125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L125" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N125" s="2" t="n">
+        <v>0.0521032783380719</v>
+      </c>
+      <c r="O125" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
         <v>6934</v>
       </c>
-      <c r="B125" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
         <is>
           <t>心誠鎂</t>
         </is>
       </c>
-      <c r="C125" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D125" s="2" t="n">
+      <c r="C126" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D126" s="2" t="n">
         <v>55.22451576500639</v>
       </c>
-      <c r="E125" s="2" t="n">
+      <c r="E126" s="2" t="n">
         <v>72.40000000000001</v>
       </c>
-      <c r="F125" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G125" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H125" s="2" t="n">
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H126" s="2" t="n">
         <v>44.57188264642103</v>
       </c>
-      <c r="I125" s="2" t="n">
+      <c r="I126" s="2" t="n">
         <v>17.69496970988244</v>
       </c>
-      <c r="J125" s="2" t="n">
+      <c r="J126" s="2" t="n">
         <v>0.4652699247750627</v>
       </c>
-      <c r="K125" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L125" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M125" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N125" s="2" t="n">
+      <c r="K126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L126" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N126" s="2" t="n">
         <v>-0.638441401587819</v>
       </c>
-      <c r="O125" s="2" t="inlineStr">
+      <c r="O126" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>
